--- a/sample/OtherEurope_Coverage.xlsx
+++ b/sample/OtherEurope_Coverage.xlsx
@@ -659,25 +659,25 @@
         </is>
       </c>
       <c r="E5">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>42.3</v>
+        <v>41.7</v>
       </c>
       <c r="H5">
         <v>100</v>
       </c>
       <c r="I5">
-        <v>42.3</v>
+        <v>41.7</v>
       </c>
       <c r="J5">
-        <v>45.1</v>
+        <v>44.4</v>
       </c>
       <c r="K5">
-        <v>56</v>
+        <v>56.7</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="O5">
-        <v>57.1</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="6">
@@ -714,25 +714,25 @@
         </is>
       </c>
       <c r="E6">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>66.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="H6">
         <v>100</v>
       </c>
       <c r="I6">
-        <v>66.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="J6">
-        <v>72.40000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="K6">
-        <v>87.3</v>
+        <v>87.8</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -744,7 +744,7 @@
         <v>0</v>
       </c>
       <c r="O6">
-        <v>96.7</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="7">
@@ -769,22 +769,22 @@
         </is>
       </c>
       <c r="E7">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>71.3</v>
+        <v>71.7</v>
       </c>
       <c r="H7">
         <v>100</v>
       </c>
       <c r="I7">
-        <v>71.3</v>
+        <v>71.7</v>
       </c>
       <c r="J7">
-        <v>75.7</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K7">
         <v>3.3</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>60.8</v>
+        <v>61.1</v>
       </c>
       <c r="O7">
         <v>93.90000000000001</v>
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="E15">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>67.5</v>
+        <v>67.2</v>
       </c>
       <c r="H15">
         <v>100</v>
@@ -1227,10 +1227,10 @@
         <v>96.7</v>
       </c>
       <c r="K15">
-        <v>90.2</v>
+        <v>91</v>
       </c>
       <c r="L15">
-        <v>93.5</v>
+        <v>94.3</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="O15">
-        <v>99.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="E38">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F38">
         <v>0</v>
       </c>
       <c r="G38">
-        <v>88.5</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="H38">
         <v>100</v>
       </c>
       <c r="I38">
-        <v>88.5</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="J38">
         <v>97.3</v>
       </c>
       <c r="K38">
-        <v>94.7</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="L38">
-        <v>96.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M38">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="E60">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -3702,10 +3702,10 @@
         <v>99.5</v>
       </c>
       <c r="K60">
-        <v>98</v>
+        <v>98.5</v>
       </c>
       <c r="L60">
-        <v>66</v>
+        <v>66.3</v>
       </c>
       <c r="M60">
         <v>0</v>
@@ -3739,13 +3739,13 @@
         </is>
       </c>
       <c r="E61">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
       <c r="G61">
-        <v>95.5</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="H61">
         <v>100</v>
@@ -3754,13 +3754,13 @@
         <v>94.90000000000001</v>
       </c>
       <c r="J61">
-        <v>97.5</v>
+        <v>98</v>
       </c>
       <c r="K61">
-        <v>93.40000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="L61">
-        <v>78.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="M61">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="E63">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -3867,16 +3867,16 @@
         <v>100</v>
       </c>
       <c r="K63">
-        <v>61.3</v>
+        <v>61.1</v>
       </c>
       <c r="L63">
-        <v>71.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="M63">
-        <v>63.8</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="N63">
-        <v>90.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O63">
         <v>100</v>
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="E65">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -3977,19 +3977,19 @@
         <v>98.90000000000001</v>
       </c>
       <c r="K65">
-        <v>98.90000000000001</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="L65">
-        <v>93.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M65">
-        <v>80.7</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="N65">
-        <v>82.3</v>
+        <v>82.8</v>
       </c>
       <c r="O65">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="66">
@@ -8898,7 +8898,7 @@
         </is>
       </c>
       <c r="E156">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -8910,16 +8910,16 @@
         <v>100</v>
       </c>
       <c r="I156">
-        <v>38.5</v>
+        <v>38.1</v>
       </c>
       <c r="J156">
-        <v>40</v>
+        <v>39.6</v>
       </c>
       <c r="K156">
         <v>0</v>
       </c>
       <c r="L156">
-        <v>86.7</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="M156">
         <v>0</v>
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="E172">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F172">
         <v>0</v>
@@ -9796,16 +9796,16 @@
         <v>95.59999999999999</v>
       </c>
       <c r="K172">
-        <v>61.7</v>
+        <v>61.5</v>
       </c>
       <c r="L172">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="M172">
         <v>14.8</v>
       </c>
       <c r="N172">
-        <v>89.09999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="O172">
         <v>98.90000000000001</v>
@@ -10658,13 +10658,13 @@
         </is>
       </c>
       <c r="E188">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F188">
         <v>1</v>
       </c>
       <c r="G188">
-        <v>57.8</v>
+        <v>57.6</v>
       </c>
       <c r="H188">
         <v>100</v>
@@ -11208,10 +11208,10 @@
         </is>
       </c>
       <c r="E198">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F198">
-        <v>69.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="G198">
         <v>0</v>
@@ -11220,10 +11220,10 @@
         <v>100</v>
       </c>
       <c r="I198">
-        <v>87.09999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="J198">
-        <v>91.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="K198">
         <v>0</v>
@@ -13683,28 +13683,28 @@
         </is>
       </c>
       <c r="E243">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F243">
         <v>0.8</v>
       </c>
       <c r="G243">
-        <v>54.6</v>
+        <v>55</v>
       </c>
       <c r="H243">
         <v>100</v>
       </c>
       <c r="I243">
-        <v>96.90000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="J243">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="K243">
         <v>0</v>
       </c>
       <c r="L243">
-        <v>77.7</v>
+        <v>78.3</v>
       </c>
       <c r="M243">
         <v>0</v>
@@ -13713,7 +13713,7 @@
         <v>0</v>
       </c>
       <c r="O243">
-        <v>99.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="244">
@@ -19997,37 +19997,37 @@
         </is>
       </c>
       <c r="E359">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F359">
         <v>100</v>
       </c>
       <c r="G359">
+        <v>100</v>
+      </c>
+      <c r="H359">
+        <v>100</v>
+      </c>
+      <c r="I359">
+        <v>100</v>
+      </c>
+      <c r="J359">
         <v>99.7</v>
       </c>
-      <c r="H359">
-        <v>100</v>
-      </c>
-      <c r="I359">
+      <c r="K359">
+        <v>66.3</v>
+      </c>
+      <c r="L359">
         <v>99.7</v>
       </c>
-      <c r="J359">
-        <v>99.3</v>
-      </c>
-      <c r="K359">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="L359">
-        <v>99.3</v>
-      </c>
       <c r="M359">
-        <v>62.2</v>
+        <v>62.4</v>
       </c>
       <c r="N359">
-        <v>98.7</v>
+        <v>99</v>
       </c>
       <c r="O359">
-        <v>99.3</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="360">
@@ -20969,22 +20969,22 @@
         </is>
       </c>
       <c r="E377">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F377">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G377">
-        <v>65</v>
+        <v>65.3</v>
       </c>
       <c r="H377">
         <v>100</v>
       </c>
       <c r="I377">
-        <v>98.3</v>
+        <v>98.7</v>
       </c>
       <c r="J377">
-        <v>98.7</v>
+        <v>99.2</v>
       </c>
       <c r="K377">
         <v>97</v>
@@ -21361,10 +21361,10 @@
         </is>
       </c>
       <c r="E385">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F385">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="G385">
         <v>0</v>
@@ -21382,7 +21382,7 @@
         <v>0</v>
       </c>
       <c r="L385">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="M385">
         <v>0</v>
@@ -21391,7 +21391,7 @@
         <v>0</v>
       </c>
       <c r="O385">
-        <v>55.2</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="386">
@@ -23836,29 +23836,29 @@
         </is>
       </c>
       <c r="E430">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F430">
+        <v>100</v>
+      </c>
+      <c r="G430">
+        <v>48.9</v>
+      </c>
+      <c r="H430">
+        <v>100</v>
+      </c>
+      <c r="I430">
         <v>99.5</v>
       </c>
-      <c r="G430">
-        <v>49.2</v>
-      </c>
-      <c r="H430">
-        <v>100</v>
-      </c>
-      <c r="I430">
+      <c r="J430">
+        <v>100</v>
+      </c>
+      <c r="K430">
+        <v>0</v>
+      </c>
+      <c r="L430">
         <v>98.90000000000001</v>
       </c>
-      <c r="J430">
-        <v>100</v>
-      </c>
-      <c r="K430">
-        <v>0</v>
-      </c>
-      <c r="L430">
-        <v>98.40000000000001</v>
-      </c>
       <c r="M430">
         <v>0</v>
       </c>
@@ -23866,7 +23866,7 @@
         <v>0</v>
       </c>
       <c r="O430">
-        <v>99.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="431">
@@ -23891,10 +23891,10 @@
         </is>
       </c>
       <c r="E431">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F431">
-        <v>98.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G431">
         <v>0</v>
@@ -23903,16 +23903,16 @@
         <v>100</v>
       </c>
       <c r="I431">
-        <v>98.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="J431">
-        <v>98.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="K431">
-        <v>73.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="L431">
-        <v>98.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="M431">
         <v>0</v>
@@ -23921,7 +23921,7 @@
         <v>0</v>
       </c>
       <c r="O431">
-        <v>99.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="432">
@@ -25651,13 +25651,13 @@
         </is>
       </c>
       <c r="E463">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F463">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="G463">
-        <v>57.7</v>
+        <v>57.9</v>
       </c>
       <c r="H463">
         <v>100</v>
@@ -25666,13 +25666,13 @@
         <v>99.5</v>
       </c>
       <c r="J463">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="K463">
         <v>0</v>
       </c>
       <c r="L463">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="M463">
         <v>0</v>
@@ -25926,10 +25926,10 @@
         </is>
       </c>
       <c r="E468">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F468">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G468">
         <v>97.5</v>
@@ -25944,19 +25944,19 @@
         <v>97.5</v>
       </c>
       <c r="K468">
-        <v>97.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="L468">
-        <v>90.90000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="M468">
         <v>0</v>
       </c>
       <c r="N468">
-        <v>61</v>
+        <v>61.2</v>
       </c>
       <c r="O468">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="469">
@@ -25981,10 +25981,10 @@
         </is>
       </c>
       <c r="E469">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F469">
-        <v>98.8</v>
+        <v>99.2</v>
       </c>
       <c r="G469">
         <v>97.09999999999999</v>
@@ -25999,19 +25999,19 @@
         <v>99.2</v>
       </c>
       <c r="K469">
-        <v>88.8</v>
+        <v>89.2</v>
       </c>
       <c r="L469">
-        <v>62.7</v>
+        <v>62.9</v>
       </c>
       <c r="M469">
-        <v>61.4</v>
+        <v>61.7</v>
       </c>
       <c r="N469">
-        <v>48.1</v>
+        <v>48.3</v>
       </c>
       <c r="O469">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="470">
